--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486457_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486457_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8939</v>
+        <v>5.7944</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8185</v>
+        <v>5.0401</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0755</v>
+        <v>0.7543</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0634</v>
+        <v>4.234</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1582</v>
+        <v>0.9669</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0948</v>
+        <v>3.2671</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008399999999999999</v>
+        <v>4.3666</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1063</v>
+        <v>0.8061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1147</v>
+        <v>3.5604</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0718</v>
+        <v>-0.1325</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0519</v>
+        <v>0.1608</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0199</v>
+        <v>-0.2933</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5225</v>
+        <v>-4.5676</v>
       </c>
       <c r="Q2" t="n">
+        <v>-6.5252</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.9576</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0877</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.1584</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.0707</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6.0403</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6.0403</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.9796</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.1596</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.4552</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.6504</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.1952</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3685</v>
+        <v>4.4058</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4722</v>
+        <v>3.5769</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1037</v>
+        <v>0.8289</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0738</v>
+        <v>-0.0634</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7822</v>
+        <v>-0.1582</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7084</v>
+        <v>0.0948</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5251</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4486</v>
+        <v>-0.1063</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765</v>
+        <v>0.1147</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4512</v>
+        <v>-0.0718</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6663</v>
+        <v>-0.0519</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7849</v>
+        <v>-0.0199</v>
       </c>
       <c r="P3" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.795</v>
+        <v>0.4915</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9047</v>
+        <v>0.9181</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1097</v>
+        <v>-0.4266</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4997</v>
+        <v>2.4552</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>2.6504</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2061</v>
+        <v>4.0841</v>
       </c>
       <c r="E4" t="n">
-        <v>1.299</v>
+        <v>1.3928</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9071</v>
+        <v>2.6914</v>
       </c>
       <c r="G4" t="n">
         <v>2.4182</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2431</v>
+        <v>0.1211</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9542</v>
+        <v>1.0479</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7111</v>
+        <v>-0.9268</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.09</v>
+        <v>3.6902</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8288</v>
+        <v>3.5781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2612</v>
+        <v>0.1121</v>
       </c>
       <c r="G5" t="n">
-        <v>4.234</v>
+        <v>1.0738</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9669</v>
+        <v>1.7822</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2671</v>
+        <v>-0.7084</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3666</v>
+        <v>2.5251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8061</v>
+        <v>2.4486</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5604</v>
+        <v>0.0765</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1325</v>
+        <v>-1.4512</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1608</v>
+        <v>-0.6663</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2933</v>
+        <v>-0.7849</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.5676</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.5252</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6168</v>
+        <v>1.1167</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0529</v>
+        <v>1.0106</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.5639</v>
+        <v>0.106</v>
       </c>
       <c r="V5" t="n">
-        <v>6.0403</v>
+        <v>1.4997</v>
       </c>
       <c r="W5" t="n">
-        <v>6.0403</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.36</v>
+        <v>2.3455</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2767</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6367</v>
+        <v>1.466</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.88</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7906</v>
+        <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0894</v>
+        <v>-0.1068</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.5324</v>
+        <v>-0.3203</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1188</v>
+        <v>0.1737</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4136</v>
+        <v>-0.494</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3476</v>
+        <v>0.3839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3282</v>
+        <v>-0.0033</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6758</v>
+        <v>0.3872</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0877</v>
+        <v>0.6315</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3878</v>
+        <v>1.2894</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3001</v>
+        <v>-0.6579</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4997</v>
+        <v>2.0854</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>2.0854</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6835</v>
+        <v>0.2056</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6896</v>
+        <v>0.2425</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0061</v>
+        <v>-0.0369</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0209</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5945</v>
+        <v>1.1167</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8242</v>
+        <v>1.3772</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2297</v>
+        <v>-0.2605</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6162</v>
+        <v>0.1636</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4183</v>
+        <v>-1.2573</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0345</v>
+        <v>1.4209</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06370000000000001</v>
+        <v>-2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1704</v>
+        <v>-0.7906</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1068</v>
+        <v>-2.0894</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3203</v>
+        <v>-2.5324</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1737</v>
+        <v>-1.1188</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.494</v>
+        <v>-1.4136</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3839</v>
+        <v>-0.3476</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0033</v>
+        <v>0.3282</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3872</v>
+        <v>-0.6758</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0979</v>
+        <v>0.8914</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.4072</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0895</v>
+        <v>-0.5158</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0854</v>
+        <v>1.4997</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0854</v>
+        <v>0.9554</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4957</v>
+        <v>-0.0824</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1075</v>
+        <v>0.4369</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6117</v>
+        <v>-0.5193</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4481</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1167</v>
+        <v>0.5387</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3531</v>
+        <v>0.6826</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3904</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2504</v>
+        <v>-0.7667</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9207</v>
+        <v>-1.6971</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6702</v>
+        <v>0.9305</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9149</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8597</v>
+        <v>1.3435</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7367</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1231</v>
+        <v>0.3833</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8449</v>
+        <v>-0.8032</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7806</v>
+        <v>-1.0163</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0643</v>
+        <v>0.2131</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5655</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4746</v>
+        <v>-0.4329</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7294</v>
+        <v>0.0349</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7452</v>
+        <v>-0.4678</v>
       </c>
       <c r="V11" t="n">
         <v>0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8745</v>
+        <v>-2.2656</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8791</v>
+        <v>-4.2085</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0046</v>
+        <v>1.9429</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2318</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5122</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3305</v>
+        <v>0.3401</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1817</v>
+        <v>-0.2434</v>
       </c>
       <c r="V12" t="n">
         <v>0.7395</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7441</v>
+        <v>16.7713</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9402</v>
+        <v>6.967600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>9.803999999999998</v>
+        <v>9.803900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.334899999999999</v>
+        <v>-3.3349</v>
       </c>
       <c r="H13" t="n">
         <v>1.6574</v>
@@ -1444,7 +1444,7 @@
         <v>-1.480599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7780999999999998</v>
+        <v>0.7780999999999993</v>
       </c>
       <c r="L13" t="n">
         <v>-2.2591</v>
@@ -1459,7 +1459,7 @@
         <v>-2.7335</v>
       </c>
       <c r="P13" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.2254</v>
@@ -1468,13 +1468,13 @@
         <v>15.2254</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9748</v>
+        <v>6.0026</v>
       </c>
       <c r="T13" t="n">
-        <v>9.1991</v>
+        <v>10.2266</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.224199999999999</v>
+        <v>-4.2241</v>
       </c>
       <c r="V13" t="n">
         <v>14.104</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8391</v>
+        <v>2.0903</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7942</v>
+        <v>1.2354</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0449</v>
+        <v>0.8549</v>
       </c>
       <c r="G14" t="n">
         <v>4.6212</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1235</v>
+        <v>0.3746</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2197</v>
+        <v>0.6609</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0963</v>
+        <v>-0.2863</v>
       </c>
       <c r="V14" t="n">
         <v>-1.818</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9694</v>
+        <v>1.5712</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3921</v>
+        <v>1.7215</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4226</v>
+        <v>-0.1503</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3377</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5893</v>
+        <v>0.1911</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7797</v>
+        <v>1.1092</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1904</v>
+        <v>-0.9181</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6603</v>
+        <v>1.0298</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2191</v>
+        <v>0.0673</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4412</v>
+        <v>0.9625</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7885</v>
+        <v>2.7609</v>
       </c>
       <c r="H16" t="n">
-        <v>0.888</v>
+        <v>1.6118</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9005</v>
+        <v>1.1491</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7377</v>
+        <v>2.1459</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6268</v>
+        <v>0.9371</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1108</v>
+        <v>1.2089</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0509</v>
+        <v>0.615</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2612</v>
+        <v>0.6748</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7897</v>
+        <v>-0.0598</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.6101</v>
+        <v>-2.3926</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8633</v>
+        <v>-1.0001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8963</v>
+        <v>0.2932</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.033</v>
+        <v>-1.2933</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.904</v>
+        <v>-0.5135</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>0.0207</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0992</v>
+        <v>-0.5342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4397</v>
+        <v>0.4798</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8268</v>
+        <v>-0.2338</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3871</v>
+        <v>0.7135</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7609</v>
+        <v>2.7885</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6118</v>
+        <v>0.888</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1491</v>
+        <v>1.9005</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1459</v>
+        <v>1.7377</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9371</v>
+        <v>0.6268</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2089</v>
+        <v>1.1108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.615</v>
+        <v>1.0509</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6748</v>
+        <v>0.2612</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0598</v>
+        <v>0.7897</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-2.6101</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.4696</v>
+        <v>-0.3172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6008</v>
+        <v>0.4434</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.8688</v>
+        <v>-0.7607</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5135</v>
+        <v>-0.904</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0207</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5342</v>
+        <v>-1.0992</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9932</v>
+        <v>-0.6874</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1268</v>
+        <v>-3.9033</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1336</v>
+        <v>3.2158</v>
       </c>
       <c r="G18" t="n">
         <v>1.1649</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1799</v>
+        <v>0.1259</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6044</v>
+        <v>-0.3809</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4245</v>
+        <v>0.5068</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0207</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8244</v>
+        <v>-1.8348</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2432</v>
+        <v>0.438</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0676</v>
+        <v>-2.2727</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8297</v>
+        <v>-0.8253</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1914</v>
+        <v>-0.4867</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6383</v>
+        <v>-0.3386</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2689</v>
+        <v>0.3478</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6752</v>
+        <v>-0.2674</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5937</v>
+        <v>0.6152</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4392</v>
+        <v>-1.1732</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4838</v>
+        <v>-0.2193</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0446</v>
+        <v>-0.9539</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5635</v>
+        <v>-1.3675</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1717</v>
+        <v>0.3076</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6082</v>
+        <v>-1.6752</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.695</v>
+        <v>-0.7294</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8902</v>
+        <v>-0.7294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5122</v>
+        <v>-2.1905</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9021</v>
+        <v>-0.0921</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6101</v>
+        <v>-2.0984</v>
       </c>
       <c r="G20" t="n">
-        <v>0.657</v>
+        <v>0.8297</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7543</v>
+        <v>0.1914</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4112</v>
+        <v>0.6383</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1366</v>
+        <v>1.2689</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6538</v>
+        <v>0.6752</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5172</v>
+        <v>0.5937</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7936</v>
+        <v>-0.4392</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1004</v>
+        <v>-0.4838</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8941</v>
+        <v>0.0446</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R20" t="n">
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8015</v>
+        <v>0.1974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>0.8364</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2536</v>
+        <v>-0.639</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0202</v>
+        <v>-1.695</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0202</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9524</v>
+        <v>-2.2887</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6796</v>
+        <v>-0.6786</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2727</v>
+        <v>-1.6101</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8253</v>
+        <v>0.657</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4867</v>
+        <v>-0.7543</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3386</v>
+        <v>1.4112</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3478</v>
+        <v>-0.1366</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2674</v>
+        <v>-0.6538</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6152</v>
+        <v>0.5172</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1732</v>
+        <v>0.7936</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2193</v>
+        <v>-0.1004</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9539</v>
+        <v>0.8941</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.4851</v>
+        <v>-0.578</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8099</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6752</v>
+        <v>-0.2536</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7294</v>
+        <v>-3.0202</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7294</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0142</v>
+        <v>-3.5577</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5771</v>
+        <v>-2.8326</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4371</v>
+        <v>-0.7251</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9705</v>
+        <v>-2.9447</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7857</v>
+        <v>-0.6051</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1849</v>
+        <v>-2.3396</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3313</v>
+        <v>-3.115</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.4843</v>
+        <v>-0.8998</v>
       </c>
       <c r="L22" t="n">
-        <v>0.153</v>
+        <v>-2.2152</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6392</v>
+        <v>0.1704</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3013</v>
+        <v>0.2947</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3379</v>
+        <v>-0.1243</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3033</v>
+        <v>-0.8841</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7112</v>
+        <v>0.2824</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4079</v>
+        <v>-1.1666</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8695</v>
+        <v>-1.469</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-1.469</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9052</v>
+        <v>-3.7477</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.062</v>
+        <v>-2.5829</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8433</v>
+        <v>-1.1648</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9447</v>
+        <v>-2.9705</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6051</v>
+        <v>-2.7857</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3396</v>
+        <v>-0.1849</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.115</v>
+        <v>-2.3313</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8998</v>
+        <v>-2.4843</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2152</v>
+        <v>0.153</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1704</v>
+        <v>-0.6392</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2947</v>
+        <v>-0.3013</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1243</v>
+        <v>-0.3379</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R23" t="n">
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2317</v>
+        <v>-0.4302</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9469</v>
+        <v>0.7054</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2847</v>
+        <v>-1.1356</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.469</v>
+        <v>-1.8695</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.469</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5718</v>
+        <v>-5.1184</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2782</v>
+        <v>-2.9429</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2936</v>
+        <v>-2.1754</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4093</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2501</v>
+        <v>0.2034</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0445</v>
+        <v>0.2908</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2056</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.2599</v>
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.7443</v>
+        <v>-14.2541</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.804000000000002</v>
+        <v>-9.804</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.940200000000001</v>
+        <v>-4.450099999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>3.334700000000001</v>
+        <v>3.334700000000002</v>
       </c>
       <c r="H25" t="n">
         <v>-1.6577</v>
       </c>
       <c r="I25" t="n">
-        <v>4.9923</v>
+        <v>4.992300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.854299999999999</v>
+        <v>1.8543</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8793</v>
+        <v>-0.8792999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>2.733499999999999</v>
+        <v>2.7335</v>
       </c>
       <c r="M25" t="n">
         <v>1.4807</v>
@@ -2404,13 +2404,13 @@
         <v>15.2253</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.975</v>
+        <v>-3.4847</v>
       </c>
       <c r="T25" t="n">
-        <v>4.2241</v>
+        <v>4.2239</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.199199999999999</v>
+        <v>-7.709</v>
       </c>
       <c r="V25" t="n">
         <v>-14.104</v>
